--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_BC PEÑÍSCOLA.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_BC PEÑÍSCOLA.xlsx
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. MONFORTE MARTINEZ</t>
+          <t>J. REY SANCHEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>-3.227999999999999</v>
+        <v>-1.7521</v>
       </c>
       <c r="E4" t="n">
-        <v>5.6654</v>
+        <v>1.0977</v>
       </c>
       <c r="F4" t="n">
-        <v>-8.8934</v>
+        <v>-2.8499</v>
       </c>
       <c r="G4" t="n">
-        <v>-9.2485</v>
+        <v>-0.2532</v>
       </c>
       <c r="H4" t="n">
-        <v>-12.8742</v>
+        <v>-5.3287</v>
       </c>
       <c r="I4" t="n">
-        <v>3.6254</v>
+        <v>5.0753</v>
       </c>
       <c r="J4" t="n">
-        <v>6.4624</v>
+        <v>10.2821</v>
       </c>
       <c r="K4" t="n">
-        <v>1.2947</v>
+        <v>2.8012</v>
       </c>
       <c r="L4" t="n">
-        <v>5.1674</v>
+        <v>7.4809</v>
       </c>
       <c r="M4" t="n">
-        <v>-15.711</v>
+        <v>-10.5355</v>
       </c>
       <c r="N4" t="n">
-        <v>-14.1687</v>
+        <v>-8.129900000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.5422</v>
+        <v>-2.4056</v>
       </c>
       <c r="P4" t="n">
-        <v>5.1313</v>
+        <v>-7.5136</v>
       </c>
       <c r="Q4" t="n">
-        <v>-14.2942</v>
+        <v>-16.6765</v>
       </c>
       <c r="R4" t="n">
-        <v>19.4252</v>
+        <v>9.1629</v>
       </c>
       <c r="S4" t="n">
-        <v>12.313</v>
+        <v>-0.5901000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>8.055199999999999</v>
+        <v>-1.3871</v>
       </c>
       <c r="U4" t="n">
-        <v>4.257499999999999</v>
+        <v>0.7969000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>-11.4237</v>
+        <v>6.6047</v>
       </c>
       <c r="W4" t="n">
-        <v>5.4419</v>
+        <v>8.879300000000001</v>
       </c>
       <c r="X4" t="n">
-        <v>-16.8654</v>
+        <v>-2.2745</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. REY SANCHEZ</t>
+          <t>R. SORO VILLANUEVA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="D5" t="n">
-        <v>-5.4377</v>
+        <v>-7.586599999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.6085</v>
+        <v>2.604900000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.8293</v>
+        <v>-10.1914</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.2532</v>
+        <v>15.1977</v>
       </c>
       <c r="H5" t="n">
-        <v>-5.3287</v>
+        <v>13.7133</v>
       </c>
       <c r="I5" t="n">
-        <v>5.0753</v>
+        <v>1.484499999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>10.2821</v>
+        <v>57.9427</v>
       </c>
       <c r="K5" t="n">
-        <v>2.8012</v>
+        <v>51.033</v>
       </c>
       <c r="L5" t="n">
-        <v>7.4809</v>
+        <v>6.9093</v>
       </c>
       <c r="M5" t="n">
-        <v>-10.5355</v>
+        <v>-42.745</v>
       </c>
       <c r="N5" t="n">
-        <v>-8.129900000000001</v>
+        <v>-37.3195</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.4056</v>
+        <v>-5.425</v>
       </c>
       <c r="P5" t="n">
-        <v>-7.5136</v>
+        <v>-31.1537</v>
       </c>
       <c r="Q5" t="n">
-        <v>-16.6765</v>
+        <v>-78.06780000000001</v>
       </c>
       <c r="R5" t="n">
-        <v>9.1629</v>
+        <v>46.9137</v>
       </c>
       <c r="S5" t="n">
-        <v>-4.2756</v>
+        <v>-1.6455</v>
       </c>
       <c r="T5" t="n">
-        <v>-4.0936</v>
+        <v>-1.0729</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1822</v>
+        <v>-0.5728000000000002</v>
       </c>
       <c r="V5" t="n">
-        <v>6.6047</v>
+        <v>10.0152</v>
       </c>
       <c r="W5" t="n">
-        <v>8.879300000000001</v>
+        <v>23.8026</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.2745</v>
+        <v>-13.7874</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. SORO VILLANUEVA</t>
+          <t>O. FORNER LUCEA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>-6.919700000000001</v>
+        <v>-7.909599999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>7.122300000000001</v>
+        <v>-6.843800000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>-14.0421</v>
+        <v>-1.0658</v>
       </c>
       <c r="G6" t="n">
-        <v>15.1977</v>
+        <v>-6.3217</v>
       </c>
       <c r="H6" t="n">
-        <v>13.7133</v>
+        <v>-3.6293</v>
       </c>
       <c r="I6" t="n">
-        <v>1.484499999999999</v>
+        <v>-2.6928</v>
       </c>
       <c r="J6" t="n">
-        <v>57.9427</v>
+        <v>-2.5583</v>
       </c>
       <c r="K6" t="n">
-        <v>51.033</v>
+        <v>-0.1550000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>6.9093</v>
+        <v>-2.4034</v>
       </c>
       <c r="M6" t="n">
-        <v>-42.745</v>
+        <v>-3.7632</v>
       </c>
       <c r="N6" t="n">
-        <v>-37.3195</v>
+        <v>-3.4742</v>
       </c>
       <c r="O6" t="n">
-        <v>-5.425</v>
+        <v>-0.2889999999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>-31.1537</v>
+        <v>-0.7330000000000001</v>
       </c>
       <c r="Q6" t="n">
-        <v>-78.06780000000001</v>
+        <v>-4.7648</v>
       </c>
       <c r="R6" t="n">
-        <v>46.9137</v>
+        <v>4.0318</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9790999999999997</v>
+        <v>-1.1453</v>
       </c>
       <c r="T6" t="n">
-        <v>3.4447</v>
+        <v>-0.7878000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>-4.423999999999999</v>
+        <v>-0.3576000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>10.0152</v>
+        <v>0.2907999999999999</v>
       </c>
       <c r="W6" t="n">
-        <v>23.8026</v>
+        <v>1.267</v>
       </c>
       <c r="X6" t="n">
-        <v>-13.7874</v>
+        <v>-0.9762</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>O. FORNER LUCEA</t>
+          <t>J. MONFORTE MARTINEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="D7" t="n">
-        <v>-8.7264</v>
+        <v>-9.8771</v>
       </c>
       <c r="E7" t="n">
-        <v>-7.3796</v>
+        <v>-0.03470000000000018</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.3468</v>
+        <v>-9.842500000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>-6.3217</v>
+        <v>-9.2485</v>
       </c>
       <c r="H7" t="n">
-        <v>-3.6293</v>
+        <v>-12.8742</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.6928</v>
+        <v>3.6254</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.5583</v>
+        <v>6.4624</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1550000000000001</v>
+        <v>1.2947</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.4034</v>
+        <v>5.1674</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.7632</v>
+        <v>-15.711</v>
       </c>
       <c r="N7" t="n">
-        <v>-3.4742</v>
+        <v>-14.1687</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2889999999999999</v>
+        <v>-1.5422</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.7330000000000001</v>
+        <v>5.1313</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.7648</v>
+        <v>-14.2942</v>
       </c>
       <c r="R7" t="n">
-        <v>4.0318</v>
+        <v>19.4252</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.9623</v>
+        <v>5.6635</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.3237</v>
+        <v>2.3553</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6388</v>
+        <v>3.3088</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2907999999999999</v>
+        <v>-11.4237</v>
       </c>
       <c r="W7" t="n">
-        <v>1.267</v>
+        <v>5.4419</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.9762</v>
+        <v>-16.8654</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. VANOUKIA</t>
+          <t>E. CIRCUNS RIVERA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>-13.8425</v>
+        <v>-13.2116</v>
       </c>
       <c r="E8" t="n">
-        <v>-12.4625</v>
+        <v>1.3258</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.38</v>
+        <v>-14.5376</v>
       </c>
       <c r="G8" t="n">
-        <v>-23.2837</v>
+        <v>-14.6748</v>
       </c>
       <c r="H8" t="n">
-        <v>-17.104</v>
+        <v>-17.8266</v>
       </c>
       <c r="I8" t="n">
-        <v>-6.180099999999999</v>
+        <v>3.151900000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>-5.6497</v>
+        <v>9.416600000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>-5.3709</v>
+        <v>4.4658</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.2788000000000006</v>
+        <v>4.950700000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>-17.634</v>
+        <v>-24.0913</v>
       </c>
       <c r="N8" t="n">
-        <v>-11.7329</v>
+        <v>-22.2923</v>
       </c>
       <c r="O8" t="n">
-        <v>-5.9009</v>
+        <v>-1.7988</v>
       </c>
       <c r="P8" t="n">
-        <v>0.000199999999999978</v>
+        <v>-0.3664</v>
       </c>
       <c r="Q8" t="n">
-        <v>-20.3417</v>
+        <v>-22.9071</v>
       </c>
       <c r="R8" t="n">
-        <v>20.3416</v>
+        <v>22.5406</v>
       </c>
       <c r="S8" t="n">
-        <v>4.9382</v>
+        <v>-4.759</v>
       </c>
       <c r="T8" t="n">
-        <v>3.0191</v>
+        <v>-3.2847</v>
       </c>
       <c r="U8" t="n">
-        <v>1.9192</v>
+        <v>-1.4744</v>
       </c>
       <c r="V8" t="n">
-        <v>4.503</v>
+        <v>6.5882</v>
       </c>
       <c r="W8" t="n">
-        <v>10.5098</v>
+        <v>18.1012</v>
       </c>
       <c r="X8" t="n">
-        <v>-6.0068</v>
+        <v>-11.513</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. MICHAEL KING</t>
+          <t>R. ROMAN MORA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D9" t="n">
-        <v>-17.0013</v>
+        <v>-14.2697</v>
       </c>
       <c r="E9" t="n">
-        <v>-10.6732</v>
+        <v>-5.5451</v>
       </c>
       <c r="F9" t="n">
-        <v>-6.328099999999999</v>
+        <v>-8.7248</v>
       </c>
       <c r="G9" t="n">
-        <v>-5.0222</v>
+        <v>9.746</v>
       </c>
       <c r="H9" t="n">
-        <v>-9.7813</v>
+        <v>3.7452</v>
       </c>
       <c r="I9" t="n">
-        <v>4.759</v>
+        <v>6.0009</v>
       </c>
       <c r="J9" t="n">
-        <v>22.8688</v>
+        <v>33.6181</v>
       </c>
       <c r="K9" t="n">
-        <v>14.8993</v>
+        <v>24.1513</v>
       </c>
       <c r="L9" t="n">
-        <v>7.9697</v>
+        <v>9.466899999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>-27.8912</v>
+        <v>-23.8722</v>
       </c>
       <c r="N9" t="n">
-        <v>-24.6806</v>
+        <v>-20.4061</v>
       </c>
       <c r="O9" t="n">
-        <v>-3.2104</v>
+        <v>-3.4661</v>
       </c>
       <c r="P9" t="n">
-        <v>-29.138</v>
+        <v>-15.7601</v>
       </c>
       <c r="Q9" t="n">
-        <v>-64.3233</v>
+        <v>-40.3166</v>
       </c>
       <c r="R9" t="n">
-        <v>35.1852</v>
+        <v>24.5564</v>
       </c>
       <c r="S9" t="n">
-        <v>13.0527</v>
+        <v>-2.8656</v>
       </c>
       <c r="T9" t="n">
-        <v>9.1386</v>
+        <v>-2.9902</v>
       </c>
       <c r="U9" t="n">
-        <v>3.914</v>
+        <v>0.1247000000000001</v>
       </c>
       <c r="V9" t="n">
-        <v>4.106100000000001</v>
+        <v>-5.3899</v>
       </c>
       <c r="W9" t="n">
-        <v>21.6424</v>
+        <v>4.1436</v>
       </c>
       <c r="X9" t="n">
-        <v>-17.5365</v>
+        <v>-9.533799999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>H. PAMUK</t>
+          <t>M. VANOUKIA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>-18.6389</v>
+        <v>-18.6682</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.579700000000001</v>
+        <v>-15.7447</v>
       </c>
       <c r="F10" t="n">
-        <v>-13.0593</v>
+        <v>-2.9234</v>
       </c>
       <c r="G10" t="n">
-        <v>-27.978</v>
+        <v>-23.2837</v>
       </c>
       <c r="H10" t="n">
-        <v>-25.5265</v>
+        <v>-17.104</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.4518</v>
+        <v>-6.180099999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>11.0187</v>
+        <v>-5.6497</v>
       </c>
       <c r="K10" t="n">
-        <v>5.225800000000001</v>
+        <v>-5.3709</v>
       </c>
       <c r="L10" t="n">
-        <v>5.7925</v>
+        <v>-0.2788000000000006</v>
       </c>
       <c r="M10" t="n">
-        <v>-38.9967</v>
+        <v>-17.634</v>
       </c>
       <c r="N10" t="n">
-        <v>-30.7523</v>
+        <v>-11.7329</v>
       </c>
       <c r="O10" t="n">
-        <v>-8.244299999999999</v>
+        <v>-5.9009</v>
       </c>
       <c r="P10" t="n">
-        <v>-9.7126</v>
+        <v>0.000199999999999978</v>
       </c>
       <c r="Q10" t="n">
-        <v>-44.5318</v>
+        <v>-20.3417</v>
       </c>
       <c r="R10" t="n">
-        <v>34.8193</v>
+        <v>20.3416</v>
       </c>
       <c r="S10" t="n">
-        <v>16.3167</v>
+        <v>0.1126000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>10.4554</v>
+        <v>-0.2633</v>
       </c>
       <c r="U10" t="n">
-        <v>5.8616</v>
+        <v>0.376</v>
       </c>
       <c r="V10" t="n">
-        <v>2.7352</v>
+        <v>4.503</v>
       </c>
       <c r="W10" t="n">
-        <v>17.4781</v>
+        <v>10.5098</v>
       </c>
       <c r="X10" t="n">
-        <v>-14.7426</v>
+        <v>-6.0068</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R. ROMAN MORA</t>
+          <t>E. NAVARRO VALDES</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D11" t="n">
-        <v>-22.1465</v>
+        <v>-21.4366</v>
       </c>
       <c r="E11" t="n">
-        <v>-10.4767</v>
+        <v>-7.6241</v>
       </c>
       <c r="F11" t="n">
-        <v>-11.6697</v>
+        <v>-13.8125</v>
       </c>
       <c r="G11" t="n">
-        <v>9.746</v>
+        <v>0.9845000000000002</v>
       </c>
       <c r="H11" t="n">
-        <v>3.7452</v>
+        <v>7.714399999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>6.0009</v>
+        <v>-6.730300000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>33.6181</v>
+        <v>27.936</v>
       </c>
       <c r="K11" t="n">
-        <v>24.1513</v>
+        <v>33.7629</v>
       </c>
       <c r="L11" t="n">
-        <v>9.466899999999999</v>
+        <v>-5.826699999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>-23.8722</v>
+        <v>-26.9515</v>
       </c>
       <c r="N11" t="n">
-        <v>-20.4061</v>
+        <v>-26.0483</v>
       </c>
       <c r="O11" t="n">
-        <v>-3.4661</v>
+        <v>-0.9032000000000002</v>
       </c>
       <c r="P11" t="n">
-        <v>-15.7601</v>
+        <v>-17.7759</v>
       </c>
       <c r="Q11" t="n">
-        <v>-40.3166</v>
+        <v>-53.511</v>
       </c>
       <c r="R11" t="n">
-        <v>24.5564</v>
+        <v>35.7351</v>
       </c>
       <c r="S11" t="n">
-        <v>-10.7423</v>
+        <v>-2.9756</v>
       </c>
       <c r="T11" t="n">
-        <v>-7.9219</v>
+        <v>-2.1443</v>
       </c>
       <c r="U11" t="n">
-        <v>-2.8201</v>
+        <v>-0.831</v>
       </c>
       <c r="V11" t="n">
-        <v>-5.3899</v>
+        <v>-1.6699</v>
       </c>
       <c r="W11" t="n">
-        <v>4.1436</v>
+        <v>20.0953</v>
       </c>
       <c r="X11" t="n">
-        <v>-9.533799999999999</v>
+        <v>-21.7652</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>E. CIRCUNS RIVERA</t>
+          <t>D. CHALATASHVILI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D12" t="n">
-        <v>-22.191</v>
+        <v>-25.6621</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.6094</v>
+        <v>-21.3473</v>
       </c>
       <c r="F12" t="n">
-        <v>-17.5816</v>
+        <v>-4.315</v>
       </c>
       <c r="G12" t="n">
-        <v>-14.6748</v>
+        <v>-13.137</v>
       </c>
       <c r="H12" t="n">
-        <v>-17.8266</v>
+        <v>-9.142200000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>3.151900000000001</v>
+        <v>-3.9948</v>
       </c>
       <c r="J12" t="n">
-        <v>9.416600000000001</v>
+        <v>-3.7268</v>
       </c>
       <c r="K12" t="n">
-        <v>4.4658</v>
+        <v>-1.9458</v>
       </c>
       <c r="L12" t="n">
-        <v>4.950700000000001</v>
+        <v>-1.7805</v>
       </c>
       <c r="M12" t="n">
-        <v>-24.0913</v>
+        <v>-9.410299999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>-22.2923</v>
+        <v>-7.196099999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.7988</v>
+        <v>-2.214</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.3664</v>
+        <v>-0.1831</v>
       </c>
       <c r="Q12" t="n">
-        <v>-22.9071</v>
+        <v>-16.4934</v>
       </c>
       <c r="R12" t="n">
-        <v>22.5406</v>
+        <v>16.31</v>
       </c>
       <c r="S12" t="n">
-        <v>-13.7378</v>
+        <v>-3.9841</v>
       </c>
       <c r="T12" t="n">
-        <v>-9.219899999999999</v>
+        <v>-3.3812</v>
       </c>
       <c r="U12" t="n">
-        <v>-4.518</v>
+        <v>-0.6029000000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>6.5882</v>
+        <v>-8.358000000000001</v>
       </c>
       <c r="W12" t="n">
-        <v>18.1012</v>
+        <v>2.2535</v>
       </c>
       <c r="X12" t="n">
-        <v>-11.513</v>
+        <v>-10.6115</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>E. NAVARRO VALDES</t>
+          <t>F. ROMAN MORA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>19</v>
       </c>
       <c r="D13" t="n">
-        <v>-27.5862</v>
+        <v>-25.7375</v>
       </c>
       <c r="E13" t="n">
-        <v>-12.3503</v>
+        <v>-17.5201</v>
       </c>
       <c r="F13" t="n">
-        <v>-15.2358</v>
+        <v>-8.217600000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9845000000000002</v>
+        <v>-14.4566</v>
       </c>
       <c r="H13" t="n">
-        <v>7.714399999999999</v>
+        <v>-5.7373</v>
       </c>
       <c r="I13" t="n">
-        <v>-6.730300000000001</v>
+        <v>-8.7196</v>
       </c>
       <c r="J13" t="n">
-        <v>27.936</v>
+        <v>-4.8521</v>
       </c>
       <c r="K13" t="n">
-        <v>33.7629</v>
+        <v>3.5133</v>
       </c>
       <c r="L13" t="n">
-        <v>-5.826699999999999</v>
+        <v>-8.3652</v>
       </c>
       <c r="M13" t="n">
-        <v>-26.9515</v>
+        <v>-9.6046</v>
       </c>
       <c r="N13" t="n">
-        <v>-26.0483</v>
+        <v>-9.250399999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.9032000000000002</v>
+        <v>-0.3544999999999998</v>
       </c>
       <c r="P13" t="n">
-        <v>-17.7759</v>
+        <v>-3.2985</v>
       </c>
       <c r="Q13" t="n">
-        <v>-53.511</v>
+        <v>-13.0114</v>
       </c>
       <c r="R13" t="n">
-        <v>35.7351</v>
+        <v>9.7128</v>
       </c>
       <c r="S13" t="n">
-        <v>-9.1248</v>
+        <v>-2.4034</v>
       </c>
       <c r="T13" t="n">
-        <v>-6.8707</v>
+        <v>-1.5677</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.2541</v>
+        <v>-0.8357</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.6699</v>
+        <v>-5.579000000000001</v>
       </c>
       <c r="W13" t="n">
-        <v>20.0953</v>
+        <v>1.9108</v>
       </c>
       <c r="X13" t="n">
-        <v>-21.7652</v>
+        <v>-7.4898</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>F. ROMAN MORA</t>
+          <t>D. MICHAEL KING</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D14" t="n">
-        <v>-28.9756</v>
+        <v>-27.0883</v>
       </c>
       <c r="E14" t="n">
-        <v>-19.6634</v>
+        <v>-18.7355</v>
       </c>
       <c r="F14" t="n">
-        <v>-9.3117</v>
+        <v>-8.352699999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>-14.4566</v>
+        <v>-5.0222</v>
       </c>
       <c r="H14" t="n">
-        <v>-5.7373</v>
+        <v>-9.7813</v>
       </c>
       <c r="I14" t="n">
-        <v>-8.7196</v>
+        <v>4.759</v>
       </c>
       <c r="J14" t="n">
-        <v>-4.8521</v>
+        <v>22.8688</v>
       </c>
       <c r="K14" t="n">
-        <v>3.5133</v>
+        <v>14.8993</v>
       </c>
       <c r="L14" t="n">
-        <v>-8.3652</v>
+        <v>7.9697</v>
       </c>
       <c r="M14" t="n">
-        <v>-9.6046</v>
+        <v>-27.8912</v>
       </c>
       <c r="N14" t="n">
-        <v>-9.250399999999999</v>
+        <v>-24.6806</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.3544999999999998</v>
+        <v>-3.2104</v>
       </c>
       <c r="P14" t="n">
-        <v>-3.2985</v>
+        <v>-29.138</v>
       </c>
       <c r="Q14" t="n">
-        <v>-13.0114</v>
+        <v>-64.3233</v>
       </c>
       <c r="R14" t="n">
-        <v>9.7128</v>
+        <v>35.1852</v>
       </c>
       <c r="S14" t="n">
-        <v>-5.6411</v>
+        <v>2.9661</v>
       </c>
       <c r="T14" t="n">
-        <v>-3.7113</v>
+        <v>1.0761</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.93</v>
+        <v>1.8895</v>
       </c>
       <c r="V14" t="n">
-        <v>-5.579000000000001</v>
+        <v>4.106100000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>1.9108</v>
+        <v>21.6424</v>
       </c>
       <c r="X14" t="n">
-        <v>-7.4898</v>
+        <v>-17.5365</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. CHALATASHVILI</t>
+          <t>A. ALVAREZ LENCINA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="D15" t="n">
-        <v>-30.1852</v>
+        <v>-28.9725</v>
       </c>
       <c r="E15" t="n">
-        <v>-24.3009</v>
+        <v>-12.3353</v>
       </c>
       <c r="F15" t="n">
-        <v>-5.8842</v>
+        <v>-16.6373</v>
       </c>
       <c r="G15" t="n">
-        <v>-13.137</v>
+        <v>-30.0411</v>
       </c>
       <c r="H15" t="n">
-        <v>-9.142200000000001</v>
+        <v>-23.3438</v>
       </c>
       <c r="I15" t="n">
-        <v>-3.9948</v>
+        <v>-6.6975</v>
       </c>
       <c r="J15" t="n">
-        <v>-3.7268</v>
+        <v>6.3885</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.9458</v>
+        <v>8.5932</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.7805</v>
+        <v>-2.2045</v>
       </c>
       <c r="M15" t="n">
-        <v>-9.410299999999999</v>
+        <v>-36.4299</v>
       </c>
       <c r="N15" t="n">
-        <v>-7.196099999999999</v>
+        <v>-31.9366</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.214</v>
+        <v>-4.4929</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.1831</v>
+        <v>2.016</v>
       </c>
       <c r="Q15" t="n">
-        <v>-16.4934</v>
+        <v>-30.0543</v>
       </c>
       <c r="R15" t="n">
-        <v>16.31</v>
+        <v>32.0701</v>
       </c>
       <c r="S15" t="n">
-        <v>-8.5069</v>
+        <v>-0.2308000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>-6.335</v>
+        <v>-0.7375</v>
       </c>
       <c r="U15" t="n">
-        <v>-2.1724</v>
+        <v>0.5070000000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>-8.358000000000001</v>
+        <v>-0.7168000000000005</v>
       </c>
       <c r="W15" t="n">
-        <v>2.2535</v>
+        <v>12.0675</v>
       </c>
       <c r="X15" t="n">
-        <v>-10.6115</v>
+        <v>-12.7841</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. ALVAREZ LENCINA</t>
+          <t>H. PAMUK</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>26</v>
       </c>
       <c r="D16" t="n">
-        <v>-31.0926</v>
+        <v>-30.231</v>
       </c>
       <c r="E16" t="n">
-        <v>-14.878</v>
+        <v>-14.0805</v>
       </c>
       <c r="F16" t="n">
-        <v>-16.2144</v>
+        <v>-16.1502</v>
       </c>
       <c r="G16" t="n">
-        <v>-30.0411</v>
+        <v>-27.978</v>
       </c>
       <c r="H16" t="n">
-        <v>-23.3438</v>
+        <v>-25.5265</v>
       </c>
       <c r="I16" t="n">
-        <v>-6.6975</v>
+        <v>-2.4518</v>
       </c>
       <c r="J16" t="n">
-        <v>6.3885</v>
+        <v>11.0187</v>
       </c>
       <c r="K16" t="n">
-        <v>8.5932</v>
+        <v>5.225800000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>-2.2045</v>
+        <v>5.7925</v>
       </c>
       <c r="M16" t="n">
-        <v>-36.4299</v>
+        <v>-38.9967</v>
       </c>
       <c r="N16" t="n">
-        <v>-31.9366</v>
+        <v>-30.7523</v>
       </c>
       <c r="O16" t="n">
-        <v>-4.4929</v>
+        <v>-8.244299999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>2.016</v>
+        <v>-9.7126</v>
       </c>
       <c r="Q16" t="n">
-        <v>-30.0543</v>
+        <v>-44.5318</v>
       </c>
       <c r="R16" t="n">
-        <v>32.0701</v>
+        <v>34.8193</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.3504</v>
+        <v>4.7245</v>
       </c>
       <c r="T16" t="n">
-        <v>-3.2803</v>
+        <v>1.9539</v>
       </c>
       <c r="U16" t="n">
-        <v>0.9298000000000001</v>
+        <v>2.7703</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.7168000000000005</v>
+        <v>2.7352</v>
       </c>
       <c r="W16" t="n">
-        <v>12.0675</v>
+        <v>17.4781</v>
       </c>
       <c r="X16" t="n">
-        <v>-12.7841</v>
+        <v>-14.7426</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>26</v>
       </c>
       <c r="D17" t="n">
-        <v>-65.78879999999999</v>
+        <v>-56.3607</v>
       </c>
       <c r="E17" t="n">
-        <v>-39.1704</v>
+        <v>-33.7988</v>
       </c>
       <c r="F17" t="n">
-        <v>-26.6186</v>
+        <v>-22.5622</v>
       </c>
       <c r="G17" t="n">
         <v>-30.8869</v>
@@ -1780,13 +1780,13 @@
         <v>33.1695</v>
       </c>
       <c r="S17" t="n">
-        <v>-18.1056</v>
+        <v>-8.6776</v>
       </c>
       <c r="T17" t="n">
-        <v>-8.680899999999999</v>
+        <v>-3.3091</v>
       </c>
       <c r="U17" t="n">
-        <v>-9.4253</v>
+        <v>-5.3686</v>
       </c>
       <c r="V17" t="n">
         <v>-7.6329</v>
@@ -1813,13 +1813,13 @@
         <v>23</v>
       </c>
       <c r="D18" t="n">
-        <v>-80.2647</v>
+        <v>-73.3716</v>
       </c>
       <c r="E18" t="n">
-        <v>-65.1108</v>
+        <v>-60.4658</v>
       </c>
       <c r="F18" t="n">
-        <v>-15.1538</v>
+        <v>-12.9059</v>
       </c>
       <c r="G18" t="n">
         <v>-47.6316</v>
@@ -1858,13 +1858,13 @@
         <v>40.8663</v>
       </c>
       <c r="S18" t="n">
-        <v>-7.985500000000001</v>
+        <v>-1.0924</v>
       </c>
       <c r="T18" t="n">
-        <v>-5.356999999999999</v>
+        <v>-0.7124</v>
       </c>
       <c r="U18" t="n">
-        <v>-2.6286</v>
+        <v>-0.3802999999999999</v>
       </c>
       <c r="V18" t="n">
         <v>-0.2744</v>
@@ -1891,13 +1891,13 @@
         <v>26</v>
       </c>
       <c r="D19" t="n">
-        <v>-339.465</v>
+        <v>-319.5751</v>
       </c>
       <c r="E19" t="n">
-        <v>-172.9156</v>
+        <v>-166.4872</v>
       </c>
       <c r="F19" t="n">
-        <v>-166.5488</v>
+        <v>-153.0888</v>
       </c>
       <c r="G19" t="n">
         <v>-154.447</v>
@@ -1915,7 +1915,7 @@
         <v>174.6427</v>
       </c>
       <c r="L19" t="n">
-        <v>32.10570000000001</v>
+        <v>32.1057</v>
       </c>
       <c r="M19" t="n">
         <v>-361.1976</v>
@@ -1936,16 +1936,16 @@
         <v>384.8405</v>
       </c>
       <c r="S19" t="n">
-        <v>-36.7908</v>
+        <v>-16.9027</v>
       </c>
       <c r="T19" t="n">
-        <v>-22.6813</v>
+        <v>-16.2529</v>
       </c>
       <c r="U19" t="n">
-        <v>-14.1114</v>
+        <v>-0.6500999999999995</v>
       </c>
       <c r="V19" t="n">
-        <v>-6.2014</v>
+        <v>-6.201400000000001</v>
       </c>
       <c r="W19" t="n">
         <v>169.8797</v>
